--- a/Dispositivos - 2026.xlsx
+++ b/Dispositivos - 2026.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -43,6 +43,10 @@
       <family val="2"/>
       <sz val="8"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -65,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -73,6 +77,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
@@ -288,7 +312,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblRedes" displayName="tblRedes" ref="A1:E5" headerRowCount="1" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblRedes" displayName="tblRedes" ref="A1:E6" headerRowCount="1" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:E5"/>
   <tableColumns count="5">
     <tableColumn id="1" name="ID da Rede" dataDxfId="13">
@@ -332,7 +356,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblClientes" displayName="tblClientes" ref="A1:I99" headerRowCount="1" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblClientes" displayName="tblClientes" ref="A1:I96" headerRowCount="1" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
   <autoFilter ref="A1:I99"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID do Cliente" dataDxfId="31">
@@ -674,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="2"/>
@@ -683,53 +707,53 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>ID da Rede</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>IP inicial</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>IP Final</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Número de Ips</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1">
+      <c r="A2" s="7">
         <f t="array" ref="A2">ROW() - ROW(tblVLans[#Headers])</f>
         <v/>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Hangar</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>192.168.68.6</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>192.168.68.254</t>
         </is>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="7">
         <f>IFERROR(VALUE(RIGHT(D2,LEN(D2)-FIND("¶",SUBSTITUTE(D2,".","¶",3))))
       - VALUE(RIGHT(C2,LEN(C2)-FIND("¶",SUBSTITUTE(C2,".","¶",3))))
       + 1,
@@ -738,26 +762,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1">
+      <c r="A3" s="7">
         <f t="array" ref="A3">ROW() - ROW(tblVLans[#Headers])</f>
         <v/>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>192.168.2.6</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>192.168.2.254</t>
         </is>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="7">
         <f>IFERROR(VALUE(RIGHT(D3,LEN(D3)-FIND("¶",SUBSTITUTE(D3,".","¶",3))))
       - VALUE(RIGHT(C3,LEN(C3)-FIND("¶",SUBSTITUTE(C3,".","¶",3))))
       + 1,
@@ -766,26 +790,26 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1">
+      <c r="A4" s="7">
         <f t="array" ref="A4">ROW() - ROW(tblVLans[#Headers])</f>
         <v/>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Servidor</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>192.168.3.6</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>192.168.3.60</t>
         </is>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="7">
         <f>IFERROR(VALUE(RIGHT(D4,LEN(D4)-FIND("¶",SUBSTITUTE(D4,".","¶",3))))
       - VALUE(RIGHT(C4,LEN(C4)-FIND("¶",SUBSTITUTE(C4,".","¶",3))))
       + 1,
@@ -794,26 +818,26 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1">
+      <c r="A5" s="7">
         <f t="array" ref="A5">ROW() - ROW(tblVLans[#Headers])</f>
         <v/>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Multimidia</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>192.168.4.2</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>192.168.4.62</t>
         </is>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="7">
         <f>IFERROR(VALUE(RIGHT(D5,LEN(D5)-FIND("¶",SUBSTITUTE(D5,".","¶",3))))
       - VALUE(RIGHT(C5,LEN(C5)-FIND("¶",SUBSTITUTE(C5,".","¶",3))))
       + 1,
@@ -822,26 +846,26 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1">
+      <c r="A6" s="7">
         <f t="array" ref="A6">ROW() - ROW(tblVLans[#Headers])</f>
         <v/>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>CamerasInternas</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>192.168.5.2</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>192.168.5.30</t>
         </is>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="7">
         <f>IFERROR(VALUE(RIGHT(D6,LEN(D6)-FIND("¶",SUBSTITUTE(D6,".","¶",3))))
       - VALUE(RIGHT(C6,LEN(C6)-FIND("¶",SUBSTITUTE(C6,".","¶",3))))
       + 1,
@@ -850,26 +874,26 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1">
+      <c r="A7" s="7">
         <f t="array" ref="A7">ROW() - ROW(tblVLans[#Headers])</f>
         <v/>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>CamerasExternas</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>192.168.6.2</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>192.168.6.30</t>
         </is>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="7">
         <f>IFERROR(VALUE(RIGHT(D7,LEN(D7)-FIND("¶",SUBSTITUTE(D7,".","¶",3))))
       - VALUE(RIGHT(C7,LEN(C7)-FIND("¶",SUBSTITUTE(C7,".","¶",3))))
       + 1,
@@ -878,26 +902,26 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1">
+      <c r="A8" s="7">
         <f t="array" ref="A8">ROW() - ROW(tblVLans[#Headers])</f>
         <v/>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Visitantes</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>192.168.10.2</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>192.168.10.30</t>
         </is>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="7">
         <f>IFERROR(VALUE(RIGHT(D8,LEN(D8)-FIND("¶",SUBSTITUTE(D8,".","¶",3))))
 - VALUE(RIGHT(C8,LEN(C8)-FIND("¶",SUBSTITUTE(C8,".","¶",3))))
 + 1,
@@ -929,7 +953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="2"/>
@@ -938,53 +962,53 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>ID da Rede</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>SSID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>IP inicial</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>IP Final</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Número de Ips</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1">
+      <c r="A2" s="7">
         <f t="array" ref="A2">ROW() - ROW(tblRedes[#Headers])</f>
         <v/>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Hangar</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>192.168.68.6</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>192.168.68.254</t>
         </is>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="7">
         <f>IFERROR(VALUE(RIGHT(D2,LEN(D2)-FIND("¶",SUBSTITUTE(D2,".","¶",3))))
       - VALUE(RIGHT(C2,LEN(C2)-FIND("¶",SUBSTITUTE(C2,".","¶",3))))
       + 1,
@@ -993,26 +1017,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1">
+      <c r="A3" s="7">
         <f t="array" ref="A3">ROW() - ROW(tblRedes[#Headers])</f>
         <v/>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Hangar_IoT</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>192.168.2.6</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>192.168.2.254</t>
         </is>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="7">
         <f>IFERROR(VALUE(RIGHT(D3,LEN(D3)-FIND("¶",SUBSTITUTE(D3,".","¶",3))))
       - VALUE(RIGHT(C3,LEN(C3)-FIND("¶",SUBSTITUTE(C3,".","¶",3))))
       + 1,
@@ -1021,26 +1045,26 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1">
+      <c r="A4" s="7">
         <f t="array" ref="A4">ROW() - ROW(tblRedes[#Headers])</f>
         <v/>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Hangar Visitante</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>192.168.10.2</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>192.168.10.30</t>
         </is>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="7">
         <f>IFERROR(VALUE(RIGHT(D4,LEN(D4)-FIND("¶",SUBSTITUTE(D4,".","¶",3))))
 - VALUE(RIGHT(C4,LEN(C4)-FIND("¶",SUBSTITUTE(C4,".","¶",3))))
 + 1,
@@ -1049,26 +1073,26 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1">
+      <c r="A5" s="7">
         <f t="array" ref="A5">ROW() - ROW(tblRedes[#Headers])</f>
         <v/>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Hangar Multimidia</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>192.168.4.2</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>192.168.4.30</t>
         </is>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="7">
         <f>IFERROR(VALUE(RIGHT(D5,LEN(D5)-FIND("¶",SUBSTITUTE(D5,".","¶",3))))
       - VALUE(RIGHT(C5,LEN(C5)-FIND("¶",SUBSTITUTE(C5,".","¶",3))))
       + 1,
@@ -1076,7 +1100,34 @@
         <v/>
       </c>
     </row>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" s="8">
+        <f>ROW() - ROW(tblRedes[#Headers])</f>
+        <v/>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Aeron</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>192.168.68.6</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>192.168.68.254</t>
+        </is>
+      </c>
+      <c r="E6" s="8">
+        <f>IFERROR(VALUE(RIGHT(D6,LEN(D6)-FIND("¶",SUBSTITUTE(D6,".","¶",3))))
+      - VALUE(RIGHT(C6,LEN(C6)-FIND("¶",SUBSTITUTE(C6,".","¶",3))))
+      + 1,
+"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="7"/>
     <row r="8"/>
     <row r="9"/>
@@ -1109,73 +1160,73 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>ID do Grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Rede</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Vlan</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>IP inicial</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>IP Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Número de Ips</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1">
+      <c r="A2" s="7">
         <f t="array" ref="A2">ROW() - ROW(tblGrupos[#Headers])</f>
         <v/>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Hangar_IoT</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>192.168.2.10</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>192.168.2.49</t>
         </is>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="7">
         <f>IFERROR(VALUE(RIGHT(F2,LEN(F2)-FIND("¶",SUBSTITUTE(F2,".","¶",3))))
       - VALUE(RIGHT(E2,LEN(E2)-FIND("¶",SUBSTITUTE(E2,".","¶",3))))
       + 1,
@@ -1184,36 +1235,36 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1">
+      <c r="A3" s="7">
         <f t="array" ref="A3">ROW() - ROW(tblGrupos[#Headers])</f>
         <v/>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Tuya</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Hangar_IoT</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>192.168.2.50</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>192.168.2.89</t>
         </is>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="7">
         <f>IFERROR(VALUE(RIGHT(F3,LEN(F3)-FIND("¶",SUBSTITUTE(F3,".","¶",3))))
 - VALUE(RIGHT(E3,LEN(E3)-FIND("¶",SUBSTITUTE(E3,".","¶",3))))
 + 1,
@@ -1222,36 +1273,36 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1">
+      <c r="A4" s="7">
         <f t="array" ref="A4">ROW() - ROW(tblGrupos[#Headers])</f>
         <v/>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Tasmota</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Hangar_IoT</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>192.168.2.90</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>192.168.2.129</t>
         </is>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="7">
         <f>IFERROR(VALUE(RIGHT(F4,LEN(F4)-FIND("¶",SUBSTITUTE(F4,".","¶",3))))
 - VALUE(RIGHT(E4,LEN(E4)-FIND("¶",SUBSTITUTE(E4,".","¶",3))))
 + 1,
@@ -1260,36 +1311,36 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1">
+      <c r="A5" s="7">
         <f t="array" ref="A5">ROW() - ROW(tblGrupos[#Headers])</f>
         <v/>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>ESPHome</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Hangar_IoT</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>192.168.2.130</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>192.168.2.169</t>
         </is>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="7">
         <f>IFERROR(VALUE(RIGHT(F5,LEN(F5)-FIND("¶",SUBSTITUTE(F5,".","¶",3))))
 - VALUE(RIGHT(E5,LEN(E5)-FIND("¶",SUBSTITUTE(E5,".","¶",3))))
 + 1,
@@ -1298,36 +1349,36 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1">
+      <c r="A6" s="7">
         <f t="array" ref="A6">ROW() - ROW(tblGrupos[#Headers])</f>
         <v/>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>SmartThings</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Hangar_IoT</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>192.168.2.170</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>192.168.2.199</t>
         </is>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="7">
         <f>IFERROR(VALUE(RIGHT(F6,LEN(F6)-FIND("¶",SUBSTITUTE(F6,".","¶",3))))
 - VALUE(RIGHT(E6,LEN(E6)-FIND("¶",SUBSTITUTE(E6,".","¶",3))))
 + 1,
@@ -1336,36 +1387,36 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1">
+      <c r="A7" s="7">
         <f t="array" ref="A7">ROW() - ROW(tblGrupos[#Headers])</f>
         <v/>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>BroadLink</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Hangar_IoT</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>192.168.2.200</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>192.168.2.209</t>
         </is>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="7">
         <f>IFERROR(VALUE(RIGHT(F7,LEN(F7)-FIND("¶",SUBSTITUTE(F7,".","¶",3))))
       - VALUE(RIGHT(E7,LEN(E7)-FIND("¶",SUBSTITUTE(E7,".","¶",3))))
       + 1,
@@ -1374,36 +1425,36 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1">
+      <c r="A8" s="7">
         <f t="array" ref="A8">ROW() - ROW(tblGrupos[#Headers])</f>
         <v/>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Wled</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Hangar_IoT</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>192.168.2.210</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>192.168.2.229</t>
         </is>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="7">
         <f>IFERROR(VALUE(RIGHT(F8,LEN(F8)-FIND("¶",SUBSTITUTE(F8,".","¶",3))))
 - VALUE(RIGHT(E8,LEN(E8)-FIND("¶",SUBSTITUTE(E8,".","¶",3))))
 + 1,
@@ -1412,36 +1463,36 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1">
+      <c r="A9" s="7">
         <f t="array" ref="A9">ROW() - ROW(tblGrupos[#Headers])</f>
         <v/>
       </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Outros</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Hangar_IoT</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>192.168.2.230</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>192.168.2.250</t>
         </is>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="7">
         <f>IFERROR(VALUE(RIGHT(F9,LEN(F9)-FIND("¶",SUBSTITUTE(F9,".","¶",3))))
       - VALUE(RIGHT(E9,LEN(E9)-FIND("¶",SUBSTITUTE(E9,".","¶",3))))
       + 1,
@@ -1450,36 +1501,36 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1">
+      <c r="A10" s="7">
         <f t="array" ref="A10">ROW() - ROW(tblGrupos[#Headers])</f>
         <v/>
       </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Alexa - Echo</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Hangar Multimidia</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>Multimidia</t>
         </is>
       </c>
-      <c r="E10" s="1" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>192.168.4.10</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>192.168.4.29</t>
         </is>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="7">
         <f>IFERROR(VALUE(RIGHT(F10,LEN(F10)-FIND("¶",SUBSTITUTE(F10,".","¶",3))))
 - VALUE(RIGHT(E10,LEN(E10)-FIND("¶",SUBSTITUTE(E10,".","¶",3))))
 + 1,
@@ -1488,36 +1539,36 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1">
+      <c r="A11" s="7">
         <f t="array" ref="A11">ROW() - ROW(tblGrupos[#Headers])</f>
         <v/>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Alexa - Fire TV</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Hangar Multimidia</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>Multimidia</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>192.168.4.30</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>192.168.4.39</t>
         </is>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="7">
         <f>IFERROR(VALUE(RIGHT(F11,LEN(F11)-FIND("¶",SUBSTITUTE(F11,".","¶",3))))
 - VALUE(RIGHT(E11,LEN(E11)-FIND("¶",SUBSTITUTE(E11,".","¶",3))))
 + 1,
@@ -1526,36 +1577,36 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1">
+      <c r="A12" s="7">
         <f t="array" ref="A12">ROW() - ROW(tblGrupos[#Headers])</f>
         <v/>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Multimídia</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Hangar Multimidia</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>Multimidia</t>
         </is>
       </c>
-      <c r="E12" s="1" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>192.168.4.40</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>192.168.4.59</t>
         </is>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="7">
         <f>IFERROR(VALUE(RIGHT(F12,LEN(F12)-FIND("¶",SUBSTITUTE(F12,".","¶",3))))
 - VALUE(RIGHT(E12,LEN(E12)-FIND("¶",SUBSTITUTE(E12,".","¶",3))))
 + 1,
@@ -1564,36 +1615,36 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1">
+      <c r="A13" s="7">
         <f t="array" ref="A13">ROW() - ROW(tblGrupos[#Headers])</f>
         <v/>
       </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Câmeras Internas</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Hangar</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>CamerasInternas</t>
         </is>
       </c>
-      <c r="E13" s="1" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>192.168.5.2</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>192.168.5.30</t>
         </is>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="7">
         <f>IFERROR(VALUE(RIGHT(F13,LEN(F13)-FIND("¶",SUBSTITUTE(F13,".","¶",3))))
       - VALUE(RIGHT(E13,LEN(E13)-FIND("¶",SUBSTITUTE(E13,".","¶",3))))
       + 1,
@@ -1602,36 +1653,36 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1">
+      <c r="A14" s="7">
         <f t="array" ref="A14">ROW() - ROW(tblGrupos[#Headers])</f>
         <v/>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Câmeras Externas</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Hangar</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>CamerasExternas</t>
         </is>
       </c>
-      <c r="E14" s="1" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>192.168.6.2</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>192.168.6.30</t>
         </is>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="7">
         <f>IFERROR(VALUE(RIGHT(F14,LEN(F14)-FIND("¶",SUBSTITUTE(F14,".","¶",3))))
       - VALUE(RIGHT(E14,LEN(E14)-FIND("¶",SUBSTITUTE(E14,".","¶",3))))
       + 1,
@@ -1640,36 +1691,36 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1">
+      <c r="A15" s="7">
         <f t="array" ref="A15">ROW() - ROW(tblGrupos[#Headers])</f>
         <v/>
       </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Celulares</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Hangar</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Hangar</t>
         </is>
       </c>
-      <c r="E15" s="1" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>192.168.68.160</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>192.168.68.179</t>
         </is>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="7">
         <f>IFERROR(VALUE(RIGHT(F15,LEN(F15)-FIND("¶",SUBSTITUTE(F15,".","¶",3))))
 - VALUE(RIGHT(E15,LEN(E15)-FIND("¶",SUBSTITUTE(E15,".","¶",3))))
 + 1,
@@ -1678,36 +1729,36 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1">
+      <c r="A16" s="7">
         <f t="array" ref="A16">ROW() - ROW(tblGrupos[#Headers])</f>
         <v/>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Computadores</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Hangar</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Hangar</t>
         </is>
       </c>
-      <c r="E16" s="1" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>192.168.68.180</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>192.168.68.199</t>
         </is>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="7">
         <f>IFERROR(VALUE(RIGHT(F16,LEN(F16)-FIND("¶",SUBSTITUTE(F16,".","¶",3))))
       - VALUE(RIGHT(E16,LEN(E16)-FIND("¶",SUBSTITUTE(E16,".","¶",3))))
       + 1,
@@ -1716,36 +1767,36 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1">
+      <c r="A17" s="7">
         <f t="array" ref="A17">ROW() - ROW(tblGrupos[#Headers])</f>
         <v/>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Servidor</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>Hangar</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>Servidor</t>
         </is>
       </c>
-      <c r="E17" s="1" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>192.168.3.6</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>192.168.3.60</t>
         </is>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" s="7">
         <f>IFERROR(VALUE(RIGHT(F17,LEN(F17)-FIND("¶",SUBSTITUTE(F17,".","¶",3))))
       - VALUE(RIGHT(E17,LEN(E17)-FIND("¶",SUBSTITUTE(E17,".","¶",3))))
       + 1,
@@ -1754,7 +1805,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="G18" s="1">
+      <c r="G18" s="7">
         <f>IFERROR(VALUE(RIGHT(F18,LEN(F18)-FIND("¶",SUBSTITUTE(F18,".","¶",3))))
 - VALUE(RIGHT(E18,LEN(E18)-FIND("¶",SUBSTITUTE(E18,".","¶",3))))
 + 1,
@@ -1781,7 +1832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I97"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="20.44140625" customWidth="1" style="1" min="1" max="1"/>
@@ -1794,86 +1845,86 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>ID do Cliente</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Ciente</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Rede</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Vlan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>AP Fixo</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Servidor</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>Proxmox</t>
         </is>
       </c>
-      <c r="D2" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D2" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Servidor</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>192.168.3.20</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Não se Aplica</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -1881,39 +1932,39 @@
       <c r="I2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Servidor</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Docker</t>
         </is>
       </c>
-      <c r="D3" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Servidor</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>192.168.3.21</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>Não se Aplica</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -1921,39 +1972,39 @@
       <c r="I3" s="1" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Servidor</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>EspHome</t>
         </is>
       </c>
-      <c r="D4" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Servidor</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>192.168.3.23</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Não se Aplica</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -1961,39 +2012,39 @@
       <c r="I4" s="1" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Servidor</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>HomeAssistant 2026</t>
         </is>
       </c>
-      <c r="D5" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Servidor</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>192.168.3.10</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Não se Aplica</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2001,39 +2052,39 @@
       <c r="I5" s="1" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Alexa - Echo</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Echo Dot Suíte</t>
         </is>
       </c>
-      <c r="D6" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Multimidia</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>192.168.4.11</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2041,39 +2092,39 @@
       <c r="I6" s="1" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Alexa - Echo</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Echo Dot Banheiro Suíte</t>
         </is>
       </c>
-      <c r="D7" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Multimidia</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>192.168.4.10</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2081,39 +2132,39 @@
       <c r="I7" s="1" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Alexa - Echo</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Echo Dot Cecília</t>
         </is>
       </c>
-      <c r="D8" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Multimidia</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>192.168.4.12</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2121,39 +2172,39 @@
       <c r="I8" s="1" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Alexa - Echo</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Echo Dot Brinquedoteca</t>
         </is>
       </c>
-      <c r="D9" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Multimidia</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>192.168.4.13</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2161,39 +2212,39 @@
       <c r="I9" s="1" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Alexa - Echo</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Echo Dot Cozinha</t>
         </is>
       </c>
-      <c r="D10" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D10" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Multimidia</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>192.168.4.14</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2201,39 +2252,39 @@
       <c r="I10" s="1" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Alexa - Echo</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Echo Dot Banheiro Social</t>
         </is>
       </c>
-      <c r="D11" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D11" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Multimidia</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>192.168.4.15</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2241,39 +2292,39 @@
       <c r="I11" s="1" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Alexa - Echo</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Echo Dot Sala de TV</t>
         </is>
       </c>
-      <c r="D12" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="D12" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Multimidia</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>192.168.4.16</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2281,39 +2332,39 @@
       <c r="I12" s="1" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Alexa - Echo</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Echo Dot Escritório</t>
         </is>
       </c>
-      <c r="D13" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="D13" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Multimidia</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>192.168.4.17</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2321,39 +2372,39 @@
       <c r="I13" s="1" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Alexa - Echo</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Echo Dot Oficina</t>
         </is>
       </c>
-      <c r="D14" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="D14" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Multimidia</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>192.168.4.18</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2361,119 +2412,119 @@
       <c r="I14" s="1" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Alexa - Fire TV</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Fire TV Suíte</t>
-        </is>
-      </c>
-      <c r="D15" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Fire Stick Suíte</t>
+        </is>
+      </c>
+      <c r="D15" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Multimidia</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>192.168.4.30</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="I15" s="1" t="n"/>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Alexa - Fire TV</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Fire TV Sala</t>
-        </is>
-      </c>
-      <c r="D16" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Fire Stick Sala de TV</t>
+        </is>
+      </c>
+      <c r="D16" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Multimidia</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>192.168.4.31</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="I16" s="1" t="n"/>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Multimídia</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>RokuTV Suíte</t>
         </is>
       </c>
-      <c r="D17" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="D17" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Multimidia</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>192.168.4.40</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2481,39 +2532,39 @@
       <c r="I17" s="1" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Tasmota</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Monitores</t>
         </is>
       </c>
-      <c r="D18" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="D18" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>192.168.2.90</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2521,39 +2572,39 @@
       <c r="I18" s="1" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="A19" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Tasmota</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Monitores</t>
         </is>
       </c>
-      <c r="D19" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="D19" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>192.168.2.91</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2561,39 +2612,39 @@
       <c r="I19" s="1" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="A20" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>Tasmota</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Luzes de Natal Externa</t>
         </is>
       </c>
-      <c r="D20" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="D20" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>192.168.2.92</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2601,39 +2652,39 @@
       <c r="I20" s="1" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="A21" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Tasmota</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Luzes de Natal Escada</t>
         </is>
       </c>
-      <c r="D21" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="D21" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>192.168.2.93</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2641,39 +2692,39 @@
       <c r="I21" s="1" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="A22" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Tasmota</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Velas de Natal</t>
         </is>
       </c>
-      <c r="D22" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="D22" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>192.168.2.94</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2681,39 +2732,39 @@
       <c r="I22" s="1" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="A23" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Tasmota</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Robo Aspirador</t>
         </is>
       </c>
-      <c r="D23" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="D23" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>192.168.2.95</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Não se Aplica</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2721,39 +2772,39 @@
       <c r="I23" s="1" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="A24" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>SmartThings</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Ar-Condicionado Suíte</t>
         </is>
       </c>
-      <c r="D24" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="D24" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>192.168.2.170</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2761,39 +2812,39 @@
       <c r="I24" s="1" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="A25" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>SmartThings</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>Ar-Condicionado Sala de TV</t>
         </is>
       </c>
-      <c r="D25" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="D25" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>192.168.2.171</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2801,39 +2852,39 @@
       <c r="I25" s="1" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="A26" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>SmartThings</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Ar-Condicionado Escritório</t>
         </is>
       </c>
-      <c r="D26" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
+      <c r="D26" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>192.168.2.172</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2841,79 +2892,79 @@
       <c r="I26" s="1" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="A27" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Computadores</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Desktop</t>
         </is>
       </c>
-      <c r="D27" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="D27" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Hangar</t>
         </is>
       </c>
-      <c r="F27" s="1" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>192.168.68.180</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="I27" s="1" t="n"/>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="A28" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Computadores</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Notebook Antonio</t>
         </is>
       </c>
-      <c r="D28" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="D28" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>Hangar</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>192.168.68.181</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>Não se Aplica</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2921,39 +2972,39 @@
       <c r="I28" s="1" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="A29" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Computadores</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Notebook Renata</t>
         </is>
       </c>
-      <c r="D29" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="D29" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>Hangar</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>192.168.68.182</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>Não se Aplica</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -2961,39 +3012,39 @@
       <c r="I29" s="1" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="A30" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Boné</t>
         </is>
       </c>
-      <c r="D30" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="D30" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>192.168.2.10</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3001,39 +3052,39 @@
       <c r="I30" s="1" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="A31" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Repelente Suíte</t>
         </is>
       </c>
-      <c r="D31" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
+      <c r="D31" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>192.168.2.11</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3041,39 +3092,39 @@
       <c r="I31" s="1" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="A32" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Repelente Sala de Jantar</t>
         </is>
       </c>
-      <c r="D32" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F32" s="1" t="inlineStr">
+      <c r="D32" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>192.168.2.12</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3081,39 +3132,39 @@
       <c r="I32" s="1" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="A33" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Luz Brinquedoteca</t>
         </is>
       </c>
-      <c r="D33" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="D33" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>192.168.2.13</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3121,39 +3172,39 @@
       <c r="I33" s="1" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="A34" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Estação de Trabalho</t>
         </is>
       </c>
-      <c r="D34" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
+      <c r="D34" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>192.168.2.14</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3161,39 +3212,39 @@
       <c r="I34" s="1" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="A35" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>Multimídia Sala</t>
         </is>
       </c>
-      <c r="D35" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F35" s="1" t="inlineStr">
+      <c r="D35" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>192.168.2.15</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3201,83 +3252,79 @@
       <c r="I35" s="1" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="A36" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Servidor HomeLab</t>
         </is>
       </c>
-      <c r="D36" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F36" s="1" t="inlineStr">
+      <c r="D36" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>192.168.2.16</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="I36" s="1" t="inlineStr">
-        <is>
-          <t>Sonoff POW; alimenta servidor Homelab+HA; UniFi/HA renomeados 2026-09-06</t>
-        </is>
-      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="A37" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>Geladeira</t>
         </is>
       </c>
-      <c r="D37" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F37" s="1" t="inlineStr">
+      <c r="D37" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>192.168.2.17</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3285,39 +3332,39 @@
       <c r="I37" s="1" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="A38" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>Bancada Cozinha</t>
         </is>
       </c>
-      <c r="D38" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F38" s="1" t="inlineStr">
+      <c r="D38" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>192.168.2.18</t>
         </is>
       </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3325,39 +3372,39 @@
       <c r="I38" s="1" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="A39" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>Desktop</t>
         </is>
       </c>
-      <c r="D39" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F39" s="1" t="inlineStr">
+      <c r="D39" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>192.168.2.19</t>
         </is>
       </c>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3365,39 +3412,39 @@
       <c r="I39" s="1" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="A40" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>Repelente Brinquedoteca</t>
         </is>
       </c>
-      <c r="D40" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F40" s="1" t="inlineStr">
+      <c r="D40" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>192.168.2.20</t>
         </is>
       </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3405,39 +3452,39 @@
       <c r="I40" s="1" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="A41" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>Luz Oficina</t>
         </is>
       </c>
-      <c r="D41" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
+      <c r="D41" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>192.168.2.21</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3445,39 +3492,39 @@
       <c r="I41" s="1" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="A42" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>Tomada Sala de TV</t>
         </is>
       </c>
-      <c r="D42" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
+      <c r="D42" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>192.168.2.22</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3485,39 +3532,39 @@
       <c r="I42" s="1" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="A43" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>Espelho Banheiro Social</t>
         </is>
       </c>
-      <c r="D43" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F43" s="1" t="inlineStr">
+      <c r="D43" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>192.168.2.23</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3525,39 +3572,39 @@
       <c r="I43" s="1" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="A44" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>Luz Suíte</t>
         </is>
       </c>
-      <c r="D44" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F44" s="1" t="inlineStr">
+      <c r="D44" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>192.168.2.24</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3565,39 +3612,39 @@
       <c r="I44" s="1" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="A45" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>Luz Banheiro Social</t>
         </is>
       </c>
-      <c r="D45" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F45" s="1" t="inlineStr">
+      <c r="D45" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>192.168.2.25</t>
         </is>
       </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3605,39 +3652,39 @@
       <c r="I45" s="1" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="A46" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>Luz Cozinha</t>
         </is>
       </c>
-      <c r="D46" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F46" s="1" t="inlineStr">
+      <c r="D46" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>192.168.2.26</t>
         </is>
       </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3645,39 +3692,39 @@
       <c r="I46" s="1" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="A47" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>Impressora 3D</t>
         </is>
       </c>
-      <c r="D47" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F47" s="1" t="inlineStr">
+      <c r="D47" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>192.168.2.27</t>
         </is>
       </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3685,39 +3732,39 @@
       <c r="I47" s="1" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="A48" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>Luz Cecília</t>
         </is>
       </c>
-      <c r="D48" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F48" s="1" t="inlineStr">
+      <c r="D48" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>192.168.2.28</t>
         </is>
       </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3725,39 +3772,39 @@
       <c r="I48" s="1" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="A49" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>Celulares</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>Edge50 Antonio</t>
         </is>
       </c>
-      <c r="D49" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E49" t="inlineStr">
+      <c r="D49" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>Hangar</t>
         </is>
       </c>
-      <c r="F49" s="1" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>192.168.68.160</t>
         </is>
       </c>
-      <c r="G49" s="1" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>Não se Aplica</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H49" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3765,39 +3812,39 @@
       <c r="I49" s="1" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>51</v>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="A50" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>Celulares</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>Egde50 Renata</t>
         </is>
       </c>
-      <c r="D50" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E50" t="inlineStr">
+      <c r="D50" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>Hangar</t>
         </is>
       </c>
-      <c r="F50" s="1" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>192.168.68.161</t>
         </is>
       </c>
-      <c r="G50" s="1" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>Não se Aplica</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H50" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3805,39 +3852,39 @@
       <c r="I50" s="1" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="A51" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>Celulares</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>A71 Antonio</t>
         </is>
       </c>
-      <c r="D51" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="D51" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>Hangar</t>
         </is>
       </c>
-      <c r="F51" s="1" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>192.168.68.162</t>
         </is>
       </c>
-      <c r="G51" s="1" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>Não se Aplica</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H51" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3845,39 +3892,39 @@
       <c r="I51" s="1" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>53</v>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="A52" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>Celulares</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>M31 Renata</t>
         </is>
       </c>
-      <c r="D52" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E52" t="inlineStr">
+      <c r="D52" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>Hangar</t>
         </is>
       </c>
-      <c r="F52" s="1" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>192.168.68.163</t>
         </is>
       </c>
-      <c r="G52" s="1" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>Não se Aplica</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H52" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3885,39 +3932,39 @@
       <c r="I52" s="1" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>54</v>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="A53" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>Celulares</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>A72 Aeron</t>
         </is>
       </c>
-      <c r="D53" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E53" t="inlineStr">
+      <c r="D53" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>Hangar</t>
         </is>
       </c>
-      <c r="F53" s="1" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>192.168.68.164</t>
         </is>
       </c>
-      <c r="G53" s="1" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>Não se Aplica</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H53" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3925,39 +3972,39 @@
       <c r="I53" s="1" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>55</v>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="A54" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>Tuya</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>Nebulosa</t>
         </is>
       </c>
-      <c r="D54" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F54" s="1" t="inlineStr">
+      <c r="D54" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>192.168.2.50</t>
         </is>
       </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -3965,39 +4012,39 @@
       <c r="I54" s="1" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="A55" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>Tuya</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>Umidificador Cecília</t>
         </is>
       </c>
-      <c r="D55" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F55" s="1" t="inlineStr">
+      <c r="D55" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>192.168.2.51</t>
         </is>
       </c>
-      <c r="G55" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -4005,39 +4052,39 @@
       <c r="I55" s="1" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="A56" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>Tuya</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>Soldador Repelente</t>
         </is>
       </c>
-      <c r="D56" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F56" s="1" t="inlineStr">
+      <c r="D56" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>192.168.2.52</t>
         </is>
       </c>
-      <c r="G56" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -4045,39 +4092,39 @@
       <c r="I56" s="1" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="A57" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>Tuya</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>Cabeceira Antonio</t>
         </is>
       </c>
-      <c r="D57" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F57" s="1" t="inlineStr">
+      <c r="D57" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>192.168.2.53</t>
         </is>
       </c>
-      <c r="G57" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -4085,39 +4132,39 @@
       <c r="I57" s="1" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>59</v>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="A58" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>Tuya</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>Cabeceira Renata</t>
         </is>
       </c>
-      <c r="D58" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F58" s="1" t="inlineStr">
+      <c r="D58" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>192.168.2.54</t>
         </is>
       </c>
-      <c r="G58" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -4125,39 +4172,39 @@
       <c r="I58" s="1" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="A59" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>Tuya</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>Portão Garagem Maior</t>
         </is>
       </c>
-      <c r="D59" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F59" s="1" t="inlineStr">
+      <c r="D59" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>192.168.2.55</t>
         </is>
       </c>
-      <c r="G59" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -4165,39 +4212,39 @@
       <c r="I59" s="1" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>61</v>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="A60" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>Tuya</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
         <is>
           <t>Portão Garagem Menor</t>
         </is>
       </c>
-      <c r="D60" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F60" s="1" t="inlineStr">
+      <c r="D60" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>192.168.2.56</t>
         </is>
       </c>
-      <c r="G60" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -4205,39 +4252,39 @@
       <c r="I60" s="1" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>62</v>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="A61" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>Tuya</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>Indicador Alarme</t>
         </is>
       </c>
-      <c r="D61" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F61" s="1" t="inlineStr">
+      <c r="D61" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>192.168.2.57</t>
         </is>
       </c>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -4245,439 +4292,439 @@
       <c r="I61" s="1" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>63</v>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="A62" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Tuya</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Termocirculador Cozinha</t>
+        </is>
+      </c>
+      <c r="D62" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>192.168.2.58</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="I62" s="1" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>Outros</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>Inkbird - ISV 200W</t>
-        </is>
-      </c>
-      <c r="D62" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F62" s="1" t="inlineStr">
-        <is>
-          <t>192.168.2.230</t>
-        </is>
-      </c>
-      <c r="G62" s="1" t="inlineStr">
-        <is>
-          <t>Não se Aplica</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="I62" s="1" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>TTLock - Gatway</t>
+        </is>
+      </c>
+      <c r="D63" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>192.168.2.231</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="I63" s="1" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>Outros</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>TTLock - Gatway</t>
-        </is>
-      </c>
-      <c r="D63" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F63" s="1" t="inlineStr">
-        <is>
-          <t>192.168.2.231</t>
-        </is>
-      </c>
-      <c r="G63" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="I63" s="1" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>65</v>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>BroadLink - Sala de TV</t>
+        </is>
+      </c>
+      <c r="D64" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>192.168.2.232</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="I64" s="1" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>Outros</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>BroadLink - Sala de TV</t>
-        </is>
-      </c>
-      <c r="D64" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>192.168.2.232</t>
-        </is>
-      </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="I64" s="1" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>BroadLink - Cecília</t>
+        </is>
+      </c>
+      <c r="D65" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>192.168.2.233</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="I65" s="1" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
         <is>
           <t>Outros</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>BroadLink - Cecília</t>
-        </is>
-      </c>
-      <c r="D65" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F65" s="1" t="inlineStr">
-        <is>
-          <t>192.168.2.233</t>
-        </is>
-      </c>
-      <c r="G65" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="I65" s="1" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>67</v>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Inversor Solar 1</t>
+        </is>
+      </c>
+      <c r="D66" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>192.168.2.234</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="I66" s="1" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
         <is>
           <t>Outros</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>Inversor Solar 1</t>
-        </is>
-      </c>
-      <c r="D66" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F66" s="1" t="inlineStr">
-        <is>
-          <t>192.168.2.234</t>
-        </is>
-      </c>
-      <c r="G66" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="I66" s="1" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Kron - Usina Solar</t>
+        </is>
+      </c>
+      <c r="D67" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>192.168.2.235</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="I67" s="1" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
         <is>
           <t>Outros</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Kron - Usina Solar</t>
-        </is>
-      </c>
-      <c r="D67" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>192.168.2.235</t>
-        </is>
-      </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="I67" s="1" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>69</v>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>Kron - QGD</t>
+        </is>
+      </c>
+      <c r="D68" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>192.168.2.236</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="I68" s="1" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>Outros</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>Kron - QGD</t>
-        </is>
-      </c>
-      <c r="D68" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F68" s="1" t="inlineStr">
-        <is>
-          <t>192.168.2.236</t>
-        </is>
-      </c>
-      <c r="G68" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="I68" s="1" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>SLZB-06</t>
+        </is>
+      </c>
+      <c r="D69" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>192.168.2.237</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="I69" s="1" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
         <is>
           <t>Outros</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>SLZB-06</t>
-        </is>
-      </c>
-      <c r="D69" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F69" s="1" t="inlineStr">
-        <is>
-          <t>192.168.2.237</t>
-        </is>
-      </c>
-      <c r="G69" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="I69" s="1" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="n">
-        <v>71</v>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Alarme Hikvision</t>
+        </is>
+      </c>
+      <c r="D70" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>192.168.2.238</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="I70" s="1" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>Outros</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>Alarme Hikvision</t>
-        </is>
-      </c>
-      <c r="D70" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F70" s="1" t="inlineStr">
-        <is>
-          <t>192.168.2.238</t>
-        </is>
-      </c>
-      <c r="G70" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="I70" s="1" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Inversor Solar 2</t>
+        </is>
+      </c>
+      <c r="D71" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>192.168.2.239</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="I71" s="1" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
         <is>
           <t>Outros</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>Inversor Solar 2</t>
-        </is>
-      </c>
-      <c r="D71" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F71" s="1" t="inlineStr">
-        <is>
-          <t>192.168.2.239</t>
-        </is>
-      </c>
-      <c r="G71" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="I71" s="1" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="n">
-        <v>73</v>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>Outros</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C72" s="9" t="inlineStr">
         <is>
           <t>Geladeira Midea</t>
         </is>
       </c>
-      <c r="D72" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F72" s="1" t="inlineStr">
+      <c r="D72" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
         <is>
           <t>192.168.2.240</t>
         </is>
       </c>
-      <c r="G72" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -4685,37 +4732,39 @@
       <c r="I72" s="1" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
-        <v>74</v>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="A73" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
         <is>
           <t>Câmeras Internas</t>
         </is>
       </c>
-      <c r="C73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E73" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>Câmera Suíte</t>
+        </is>
+      </c>
+      <c r="D73" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>CamerasInternas</t>
         </is>
       </c>
-      <c r="F73" s="1" t="inlineStr">
+      <c r="F73" s="7" t="inlineStr">
         <is>
           <t>192.168.5.10</t>
         </is>
       </c>
-      <c r="G73" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -4723,39 +4772,39 @@
       <c r="I73" s="1" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
-        <v>75</v>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="A74" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
         <is>
           <t>Câmeras Internas</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" s="9" t="inlineStr">
         <is>
           <t>Câmera Cecília</t>
         </is>
       </c>
-      <c r="D74" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E74" t="inlineStr">
+      <c r="D74" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>CamerasInternas</t>
         </is>
       </c>
-      <c r="F74" s="1" t="inlineStr">
+      <c r="F74" s="7" t="inlineStr">
         <is>
           <t>192.168.5.11</t>
         </is>
       </c>
-      <c r="G74" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -4763,39 +4812,39 @@
       <c r="I74" s="1" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="A75" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
         <is>
           <t>Câmeras Internas</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>Câmera Brinquedoteca</t>
         </is>
       </c>
-      <c r="D75" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E75" t="inlineStr">
+      <c r="D75" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>CamerasInternas</t>
         </is>
       </c>
-      <c r="F75" s="1" t="inlineStr">
+      <c r="F75" s="7" t="inlineStr">
         <is>
           <t>192.168.5.12</t>
         </is>
       </c>
-      <c r="G75" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -4803,39 +4852,39 @@
       <c r="I75" s="1" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="A76" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
         <is>
           <t>Câmeras Externas</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C76" s="9" t="inlineStr">
         <is>
           <t>Câmera Portão</t>
         </is>
       </c>
-      <c r="D76" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E76" t="inlineStr">
+      <c r="D76" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
         <is>
           <t>CamerasExternas</t>
         </is>
       </c>
-      <c r="F76" s="1" t="inlineStr">
+      <c r="F76" s="7" t="inlineStr">
         <is>
           <t>192.168.6.10</t>
         </is>
       </c>
-      <c r="G76" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -4843,29 +4892,29 @@
       <c r="I76" s="1" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
-        <v>78</v>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="A77" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
         <is>
           <t>Câmeras Externas</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>Câmera Garagem</t>
         </is>
       </c>
-      <c r="D77" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E77" t="inlineStr">
+      <c r="D77" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>CamerasExternas</t>
         </is>
       </c>
-      <c r="F77" s="1" t="inlineStr">
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>192.168.6.11</t>
         </is>
@@ -4873,39 +4922,39 @@
       <c r="I77" s="1" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="A78" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
         <is>
           <t>Wled</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C78" s="9" t="inlineStr">
         <is>
           <t>Letreiro Natal</t>
         </is>
       </c>
-      <c r="D78" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F78" s="1" t="inlineStr">
+      <c r="D78" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
         <is>
           <t>192.168.2.210</t>
         </is>
       </c>
-      <c r="G78" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -4913,39 +4962,39 @@
       <c r="I78" s="1" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="A79" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
         <is>
           <t>ESPHome</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>Bancada Oficina</t>
         </is>
       </c>
-      <c r="D79" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F79" s="1" t="inlineStr">
+      <c r="D79" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>192.168.2.130</t>
         </is>
       </c>
-      <c r="G79" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -4953,39 +5002,39 @@
       <c r="I79" s="1" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
-        <v>81</v>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="A80" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
         <is>
           <t>ESPHome</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C80" s="9" t="inlineStr">
         <is>
           <t>Forno Área Gourmet</t>
         </is>
       </c>
-      <c r="D80" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
+      <c r="D80" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
         <is>
           <t>192.168.2.131</t>
         </is>
       </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -4993,39 +5042,39 @@
       <c r="I80" s="1" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
-        <v>82</v>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="A81" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
         <is>
           <t>ESPHome</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C81" s="9" t="inlineStr">
         <is>
           <t>Jardim Japonês</t>
         </is>
       </c>
-      <c r="D81" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F81" s="1" t="inlineStr">
+      <c r="D81" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
         <is>
           <t>192.168.2.132</t>
         </is>
       </c>
-      <c r="G81" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -5033,39 +5082,39 @@
       <c r="I81" s="1" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
-        <v>83</v>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="A82" s="7" t="n">
+        <v>84</v>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
         <is>
           <t>ESPHome</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C82" s="9" t="inlineStr">
         <is>
           <t>Aquecedor Solar</t>
         </is>
       </c>
-      <c r="D82" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F82" s="1" t="inlineStr">
+      <c r="D82" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
         <is>
           <t>192.168.2.133</t>
         </is>
       </c>
-      <c r="G82" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -5073,39 +5122,39 @@
       <c r="I82" s="1" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
-        <v>84</v>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="A83" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
         <is>
           <t>ESPHome</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>Ar Condicionado - Quarto Cecília</t>
         </is>
       </c>
-      <c r="D83" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F83" s="1" t="inlineStr">
+      <c r="D83" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
         <is>
           <t>192.168.2.134</t>
         </is>
       </c>
-      <c r="G83" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -5113,39 +5162,39 @@
       <c r="I83" s="1" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
-        <v>85</v>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="A84" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
         <is>
           <t>ESPHome</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C84" s="9" t="inlineStr">
         <is>
           <t>Caixa d´agua</t>
         </is>
       </c>
-      <c r="D84" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F84" s="1" t="inlineStr">
+      <c r="D84" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
         <is>
           <t>192.168.2.135</t>
         </is>
       </c>
-      <c r="G84" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -5153,39 +5202,39 @@
       <c r="I84" s="1" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
-        <v>86</v>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="A85" s="7" t="n">
+        <v>87</v>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
         <is>
           <t>ESPHome</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C85" s="9" t="inlineStr">
         <is>
           <t>Chuveiro Suíte</t>
         </is>
       </c>
-      <c r="D85" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F85" s="1" t="inlineStr">
+      <c r="D85" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
         <is>
           <t>192.168.2.136</t>
         </is>
       </c>
-      <c r="G85" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -5193,39 +5242,39 @@
       <c r="I85" s="1" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
-        <v>87</v>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="A86" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
         <is>
           <t>ESPHome</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C86" s="9" t="inlineStr">
         <is>
           <t>Interfone</t>
         </is>
       </c>
-      <c r="D86" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F86" s="1" t="inlineStr">
+      <c r="D86" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
         <is>
           <t>192.168.2.137</t>
         </is>
       </c>
-      <c r="G86" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -5233,39 +5282,39 @@
       <c r="I86" s="1" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="A87" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
         <is>
           <t>ESPHome</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="C87" s="9" t="inlineStr">
         <is>
           <t>LD2410 Brinquedoteca</t>
         </is>
       </c>
-      <c r="D87" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F87" s="1" t="inlineStr">
+      <c r="D87" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
         <is>
           <t>192.168.2.138</t>
         </is>
       </c>
-      <c r="G87" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr">
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -5273,39 +5322,39 @@
       <c r="I87" s="1" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="A88" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
         <is>
           <t>ESPHome</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C88" s="9" t="inlineStr">
         <is>
           <t>LD2410 Quarto da Cecília</t>
         </is>
       </c>
-      <c r="D88" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F88" s="1" t="inlineStr">
+      <c r="D88" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>192.168.2.139</t>
         </is>
       </c>
-      <c r="G88" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -5313,39 +5362,39 @@
       <c r="I88" s="1" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="A89" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
         <is>
           <t>ESPHome</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr">
         <is>
           <t>Ventilador Sala de Jantar</t>
         </is>
       </c>
-      <c r="D89" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F89" s="1" t="inlineStr">
+      <c r="D89" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
         <is>
           <t>192.168.2.140</t>
         </is>
       </c>
-      <c r="G89" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H89" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -5353,39 +5402,39 @@
       <c r="I89" s="1" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="A90" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
         <is>
           <t>ESPHome</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C90" s="9" t="inlineStr">
         <is>
           <t>LD2410 Escritório</t>
         </is>
       </c>
-      <c r="D90" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F90" s="1" t="inlineStr">
+      <c r="D90" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
         <is>
           <t>192.168.2.141</t>
         </is>
       </c>
-      <c r="G90" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -5393,34 +5442,34 @@
       <c r="I90" s="1" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="A91" s="7" t="n">
+        <v>93</v>
+      </c>
+      <c r="B91" s="9" t="inlineStr">
         <is>
           <t>ESPHome</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C91" s="9" t="inlineStr">
         <is>
           <t>Balança Cecília</t>
         </is>
       </c>
-      <c r="D91" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F91" s="1" t="inlineStr">
+      <c r="D91" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
         <is>
           <t>192.168.2.142</t>
         </is>
       </c>
-      <c r="G91" s="1" t="inlineStr">
+      <c r="G91" s="7" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -5428,39 +5477,39 @@
       <c r="I91" s="1" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="A92" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
         <is>
           <t>ESPHome</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C92" s="9" t="inlineStr">
         <is>
           <t>Alarme</t>
         </is>
       </c>
-      <c r="D92" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F92" s="1" t="inlineStr">
+      <c r="D92" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
         <is>
           <t>192.168.2.143</t>
         </is>
       </c>
-      <c r="G92" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -5468,39 +5517,39 @@
       <c r="I92" s="1" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="A93" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
         <is>
           <t>ESPHome</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C93" s="9" t="inlineStr">
         <is>
           <t>Gás Cozinha</t>
         </is>
       </c>
-      <c r="D93" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F93" s="1" t="inlineStr">
+      <c r="D93" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
         <is>
           <t>192.168.2.144</t>
         </is>
       </c>
-      <c r="G93" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="inlineStr">
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H93" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -5508,39 +5557,39 @@
       <c r="I93" s="1" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="A94" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
         <is>
           <t>ESPHome</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C94" s="9" t="inlineStr">
         <is>
           <t>Hidrômetro Entrada</t>
         </is>
       </c>
-      <c r="D94" s="1">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F94" s="1" t="inlineStr">
+      <c r="D94" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
         <is>
           <t>192.168.2.146</t>
         </is>
       </c>
-      <c r="G94" s="1" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
@@ -5548,122 +5597,83 @@
       <c r="I94" s="1" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" t="n">
-        <v>96</v>
-      </c>
-      <c r="B95" t="inlineStr">
+      <c r="A95" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>Alexa - Echo</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>Echo Show Sala de Jantar</t>
         </is>
       </c>
-      <c r="D95">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E95" t="inlineStr">
+      <c r="D95" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>Multimidia</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F95" s="7" t="inlineStr">
         <is>
           <t>192.168.4.19</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
-        <v>97</v>
-      </c>
-      <c r="B96" t="inlineStr">
+      <c r="A96" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>Sonoff</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>Estante Aviões</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>IoT</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
+      <c r="D96" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>192.168.2.29</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>98</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Alexa - Fire TV</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Fire Stick Sala de TV</t>
-        </is>
-      </c>
-      <c r="D97">
-        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
-        <v/>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Hangar</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>192.168.68.183</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>UniFi 2026-09-06: MAC b8:5f:98:37:a2:6b no Hangar (.183); alinhar VLAN Multimidia/IP fixo se for definitivo</t>
-        </is>
-      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">

--- a/Dispositivos - 2026.xlsx
+++ b/Dispositivos - 2026.xlsx
@@ -356,7 +356,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblClientes" displayName="tblClientes" ref="A1:I96" headerRowCount="1" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblClientes" displayName="tblClientes" ref="A1:I98" headerRowCount="1" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
   <autoFilter ref="A1:I99"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID do Cliente" dataDxfId="31">
@@ -929,13 +929,6 @@
         <v/>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16">
       <c r="C16" s="2" t="n"/>
     </row>
@@ -1128,12 +1121,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
     <row r="13">
       <c r="C13" s="2" t="n"/>
     </row>
@@ -1832,7 +1819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="20.44140625" customWidth="1" style="1" min="1" max="1"/>
@@ -2449,7 +2436,7 @@
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="I15" s="4" t="n"/>
+      <c r="I15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -2489,7 +2476,7 @@
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="I16" s="4" t="n"/>
+      <c r="I16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -2929,7 +2916,7 @@
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="I27" s="4" t="n"/>
+      <c r="I27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -3289,7 +3276,7 @@
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="I36" s="4" t="n"/>
+      <c r="I36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -5673,7 +5660,95 @@
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="I96" s="4" t="n"/>
+      <c r="I96" s="7" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>Servidor</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>AdGuard Backup</t>
+        </is>
+      </c>
+      <c r="D97" s="7">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>Servidor</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>192.168.3.22</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>Não se Aplica</t>
+        </is>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="I97" s="1" t="inlineStr">
+        <is>
+          <t>Pi Zero 2 W, MAC e4:5f:01:8f:21:d9. Wi-Fi Hangar com override UniFi para VLAN Servidor. DNS secundário.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>100</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Tuya</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Relógio Suíte</t>
+        </is>
+      </c>
+      <c r="D98">
+        <f>IF(ISERROR(INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0))),"",INDEX(tblGrupos[Rede],MATCH(tblClientes[[#This Row],[Plataforma]],tblGrupos[Plataforma],0)))</f>
+        <v/>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>192.168.2.59</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>MAC c0:f8:53:65:b9:77; Tuya eb3f4780d62224fe1epmtg; LocalTuya</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="3">
